--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>93425</v>
+        <v>93428</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>92230</v>
+        <v>92233</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>136114149</v>
       </c>
       <c r="B94" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>136114151</v>
       </c>
       <c r="B98" t="n">
-        <v>89261</v>
+        <v>89263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136114159</v>
       </c>
       <c r="B118" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>136114166</v>
       </c>
       <c r="B119" t="n">
-        <v>110313</v>
+        <v>110316</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>136114156</v>
       </c>
       <c r="B122" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92350</v>
+        <v>92353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136114159</v>
       </c>
       <c r="B118" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>136114166</v>
       </c>
       <c r="B119" t="n">
-        <v>110316</v>
+        <v>110317</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>136114156</v>
       </c>
       <c r="B122" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92353</v>
+        <v>92354</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92056</v>
+        <v>92061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92056</v>
+        <v>92061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>136114167</v>
       </c>
       <c r="B30" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>136114162</v>
       </c>
       <c r="B76" t="n">
-        <v>79543</v>
+        <v>79545</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>93429</v>
+        <v>93434</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>92234</v>
+        <v>92239</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>136114149</v>
       </c>
       <c r="B94" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>136114151</v>
       </c>
       <c r="B98" t="n">
-        <v>89263</v>
+        <v>89265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>136114145</v>
       </c>
       <c r="B99" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>136114147</v>
       </c>
       <c r="B104" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>136114150</v>
       </c>
       <c r="B108" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>136331397</v>
       </c>
       <c r="B109" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>136114152</v>
       </c>
       <c r="B114" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136114159</v>
       </c>
       <c r="B118" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>136114166</v>
       </c>
       <c r="B119" t="n">
-        <v>110317</v>
+        <v>110322</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>136114156</v>
       </c>
       <c r="B122" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>136114148</v>
       </c>
       <c r="B126" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>136114154</v>
       </c>
       <c r="B129" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92354</v>
+        <v>92359</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92061</v>
+        <v>92063</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92061</v>
+        <v>92063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92063</v>
+        <v>92065</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
